--- a/seed/dishes.xlsx
+++ b/seed/dishes.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1003"/>
+  <dimension ref="A1:I1008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -32620,6 +32620,166 @@
         <v>100</v>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Мясо курицы</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Птица</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>курица, куриное мясо, курятина, мясо курицы</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>190</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Мясо индейки</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Птица</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>индейка, индюшатина, мясо индейки</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Говядина</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Мясо</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>мясо говядина, говяжье мясо</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Свинина</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Мясо</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>мясо свинина, свиное мясо</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>260</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Баранина</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Мясо</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>мясо баранина, баранье мясо</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>258</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I308"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
